--- a/sampleprojects/Poker/excel/Poker.xlsx
+++ b/sampleprojects/Poker/excel/Poker.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
   <si>
     <t>DT: Poker Decision</t>
   </si>
@@ -48,6 +48,9 @@
     <t/>
   </si>
   <si>
+    <t>add new decision entity to context of this table; set decision.player_id = player.id; set decision.archetype = player.archetype; add "Evaluating decision for " + player.name + " (" + player.archetype + ") with hand strength " + player.hand_strength to game.audit_trail;</t>
+  </si>
+  <si>
     <t>CONDITIONS: COMMENTS</t>
   </si>
   <si>
@@ -162,7 +165,27 @@
     <t>TAG decision logic with if-else</t>
   </si>
   <si>
-    <t>Decide based on hand strength and situation</t>
+    <t>if player.hand_strength &gt;= 0.70 then
+  set decision.action = "RAISE";
+  set decision.raise_amount = game.big_blind * 3;
+  set decision.reasoning = "TAG: Strong hand, RAISE 3x BB";
+endif
+if decision.action is null and player.hand_strength &gt;= 0.50 and player.pot_odds &lt; player.hand_strength * 0.8 then
+  set decision.action = "CALL";
+  set decision.reasoning = "TAG: Medium hand with good pot odds, CALL";
+endif
+if decision.action is null and player.hand_strength &gt;= 0.50 and player.can_check then
+  set decision.action = "CHECK";
+  set decision.reasoning = "TAG: Medium hand, poor odds, CHECK";
+endif
+if decision.action is null and player.hand_strength &lt; 0.50 and player.can_check then
+  set decision.action = "CHECK";
+  set decision.reasoning = "TAG: Weak hand, CHECK for free card";
+endif
+if decision.action is null then
+  set decision.action = "FOLD";
+  set decision.reasoning = "TAG: Default FOLD";
+endif</t>
   </si>
   <si>
     <t>TAG decision logic</t>
@@ -189,7 +212,7 @@
     <t>Position is late or button</t>
   </si>
   <si>
-    <t>player.position is "late" or "button"</t>
+    <t>player.position is equal to "late" or player.position is equal to "button"</t>
   </si>
   <si>
     <t>Hand strength &gt;= 25%</t>
@@ -207,25 +230,25 @@
     <t>RAISE - Strong hand or position play</t>
   </si>
   <si>
-    <t>Set action to RAISE</t>
+    <t>set decision.action = "RAISE"; set decision.raise_amount = game.big_blind * 2.5; set decision.reasoning = "LAG: Hand &gt;= 50% or good position with &gt;= 25%, RAISE";</t>
   </si>
   <si>
     <t>CHECK - Weak hand in position</t>
   </si>
   <si>
-    <t>Set action to CHECK</t>
+    <t>set decision.action = "CHECK"; set decision.reasoning = "LAG: Weak hand in position, CHECK for free card";</t>
   </si>
   <si>
     <t>CALL - Marginal hand out of position</t>
   </si>
   <si>
-    <t>Set action to CALL</t>
+    <t>set decision.action = "CALL"; set decision.reasoning = "LAG: Marginal hand (&gt;= 25%) out of position, CALL";</t>
   </si>
   <si>
     <t>FOLD - Very weak hand</t>
   </si>
   <si>
-    <t>Set action to FOLD</t>
+    <t>set decision.action = "FOLD"; set decision.reasoning = "LAG: Weak hand (less than 25%) out of position, FOLD";</t>
   </si>
   <si>
     <t>Strong hand - raise</t>
@@ -267,15 +290,27 @@
     <t>RAISE - Only with monster hands</t>
   </si>
   <si>
+    <t>set decision.action = "RAISE"; set decision.raise_amount = game.big_blind * 2; set decision.reasoning = "Rock: Monster hand (&gt;= 85%), RAISE (rare for Rock)";</t>
+  </si>
+  <si>
     <t>CALL - Strong hand, play it safe</t>
   </si>
   <si>
+    <t>set decision.action = "CALL"; set decision.reasoning = "Rock: Strong hand (60-85%), CALL to see the showdown";</t>
+  </si>
+  <si>
     <t>CHECK - Weak hand, free card</t>
   </si>
   <si>
+    <t>set decision.action = "CHECK"; set decision.reasoning = "Rock: Weak hand (less than 60%), CHECK for free card";</t>
+  </si>
+  <si>
     <t>FOLD - Weak hand with bet</t>
   </si>
   <si>
+    <t>set decision.action = "FOLD"; set decision.reasoning = "Rock: Weak hand (less than 60%) facing a bet, FOLD";</t>
+  </si>
+  <si>
     <t>Monster hand - rare raise</t>
   </si>
   <si>
@@ -312,15 +347,27 @@
     <t>CALL - Any hand with some value</t>
   </si>
   <si>
+    <t>set decision.action = "CALL"; set decision.reasoning = "Calling Station: Any hand &gt;= 20%, CALL (love to see showdowns)";</t>
+  </si>
+  <si>
     <t>CALL - Small bet is worth calling</t>
   </si>
   <si>
+    <t>set decision.action = "CALL"; set decision.reasoning = "Calling Station: Small bet, CALL (too cheap to fold)";</t>
+  </si>
+  <si>
     <t>CHECK - Weak hand but free</t>
   </si>
   <si>
+    <t>set decision.action = "CHECK"; set decision.reasoning = "Calling Station: Weak hand but can check, CHECK";</t>
+  </si>
+  <si>
     <t>FOLD - Very weak with big bet</t>
   </si>
   <si>
+    <t>set decision.action = "FOLD"; set decision.reasoning = "Calling Station: Very weak hand (less than 20%) with large bet, FOLD (reluctantly)";</t>
+  </si>
+  <si>
     <t>Any value - call</t>
   </si>
   <si>
@@ -358,6 +405,21 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>Collect</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Q Type</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>Reference</t>
   </si>
   <si>
     <t>decision</t>
@@ -1147,7 +1209,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -1168,11 +1230,11 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -1228,13 +1290,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>8</v>
@@ -1287,16 +1349,16 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>8</v>
@@ -1346,10 +1408,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
@@ -1358,7 +1420,7 @@
         <v>8</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>8</v>
@@ -1405,10 +1467,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
@@ -1420,7 +1482,7 @@
         <v>8</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>8</v>
@@ -1461,11 +1523,11 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
@@ -1521,13 +1583,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>8</v>
@@ -1580,16 +1642,16 @@
         <v>2</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>8</v>
@@ -1639,10 +1701,10 @@
         <v>3</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -1651,7 +1713,7 @@
         <v>8</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>8</v>
@@ -1698,10 +1760,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
@@ -1713,7 +1775,7 @@
         <v>8</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>8</v>
@@ -1757,22 +1819,22 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>8</v>
@@ -1813,11 +1875,11 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -1873,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>8</v>
@@ -1932,7 +1994,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>8</v>
@@ -1991,7 +2053,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>8</v>
@@ -2050,7 +2112,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>8</v>
@@ -2133,7 +2195,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2156,7 +2218,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2179,7 +2241,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2202,7 +2264,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2275,11 +2337,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -2335,13 +2397,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>8</v>
@@ -2391,11 +2453,11 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -2451,13 +2513,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>8</v>
@@ -2507,11 +2569,11 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -2567,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>8</v>
@@ -2649,7 +2711,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2695,7 +2757,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2718,7 +2780,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2791,11 +2853,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -2851,25 +2913,25 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>8</v>
@@ -2910,25 +2972,25 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>8</v>
@@ -2969,25 +3031,25 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>8</v>
@@ -3028,10 +3090,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
@@ -3040,7 +3102,7 @@
         <v>8</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>8</v>
@@ -3084,11 +3146,11 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -3144,16 +3206,16 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>8</v>
@@ -3203,10 +3265,10 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -3215,7 +3277,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>8</v>
@@ -3262,10 +3324,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -3277,7 +3339,7 @@
         <v>8</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>8</v>
@@ -3321,10 +3383,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -3339,7 +3401,7 @@
         <v>8</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>8</v>
@@ -3377,11 +3439,11 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -3437,7 +3499,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>8</v>
@@ -3496,7 +3558,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>8</v>
@@ -3555,7 +3617,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>8</v>
@@ -3614,7 +3676,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>8</v>
@@ -3673,7 +3735,7 @@
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>8</v>
@@ -3755,7 +3817,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3801,7 +3863,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3824,7 +3886,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -3897,11 +3959,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -3957,22 +4019,22 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>8</v>
@@ -4016,22 +4078,22 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -4075,10 +4137,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>8</v>
@@ -4087,10 +4149,10 @@
         <v>8</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -4131,11 +4193,11 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -4191,13 +4253,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>8</v>
@@ -4250,16 +4312,16 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>8</v>
@@ -4309,10 +4371,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -4321,7 +4383,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>8</v>
@@ -4368,10 +4430,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -4383,7 +4445,7 @@
         <v>8</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>8</v>
@@ -4424,11 +4486,11 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -4484,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>8</v>
@@ -4543,7 +4605,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>8</v>
@@ -4602,7 +4664,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>8</v>
@@ -4661,7 +4723,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>8</v>
@@ -4743,7 +4805,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4789,7 +4851,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -4812,7 +4874,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -4885,11 +4947,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -4945,22 +5007,22 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>8</v>
@@ -5004,22 +5066,22 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -5063,10 +5125,10 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>8</v>
@@ -5075,10 +5137,10 @@
         <v>8</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -5119,11 +5181,11 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -5179,13 +5241,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>8</v>
@@ -5238,16 +5300,16 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>8</v>
@@ -5297,10 +5359,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -5309,7 +5371,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>8</v>
@@ -5356,10 +5418,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -5371,7 +5433,7 @@
         <v>8</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>8</v>
@@ -5412,11 +5474,11 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -5472,7 +5534,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>8</v>
@@ -5531,7 +5593,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>8</v>
@@ -5590,7 +5652,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>8</v>
@@ -5649,7 +5711,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>8</v>
@@ -5731,45 +5793,65 @@
     <col customWidth="true" max="5" min="5" width="18"/>
     <col customWidth="true" max="7" min="6" width="8"/>
     <col customWidth="true" max="8" min="8" width="55"/>
+    <col customWidth="true" max="9" min="9" width="8"/>
+    <col customWidth="true" max="10" min="10" width="30"/>
+    <col customWidth="true" max="11" min="11" width="16"/>
+    <col customWidth="true" max="12" min="12" width="30"/>
+    <col customWidth="true" max="13" min="13" width="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -5777,16 +5859,21 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
@@ -5798,10 +5885,25 @@
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>118</v>
+        <v>132</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -5809,10 +5911,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
@@ -5824,10 +5926,25 @@
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>120</v>
+        <v>134</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -5835,10 +5952,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
@@ -5850,10 +5967,25 @@
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>122</v>
+        <v>136</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -5861,25 +5993,40 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>126</v>
+        <v>140</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -5887,10 +6034,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
@@ -5902,18 +6049,33 @@
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>128</v>
+        <v>142</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -5921,31 +6083,51 @@
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>117</v>
-      </c>
       <c r="H10" s="16" t="s">
-        <v>133</v>
+        <v>147</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -5953,25 +6135,40 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>137</v>
+        <v>151</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -5979,25 +6176,40 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>124</v>
-      </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>139</v>
+        <v>153</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -6005,13 +6217,13 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>8</v>
@@ -6020,10 +6232,25 @@
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>142</v>
+        <v>156</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -6031,10 +6258,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
@@ -6043,13 +6270,28 @@
         <v>8</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>144</v>
+        <v>158</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -6057,25 +6299,40 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>147</v>
+        <v>161</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -6083,13 +6340,13 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>8</v>
@@ -6098,10 +6355,25 @@
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>150</v>
+        <v>164</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -6109,33 +6381,48 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>152</v>
+        <v>166</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -6143,31 +6430,51 @@
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>155</v>
+        <v>169</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -6175,25 +6482,40 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>159</v>
+        <v>173</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -6201,25 +6523,40 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>161</v>
+        <v>175</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -6227,10 +6564,10 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>8</v>
@@ -6239,13 +6576,28 @@
         <v>8</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>162</v>
+        <v>176</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -6253,25 +6605,40 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>164</v>
+        <v>178</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -6279,10 +6646,10 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>8</v>
@@ -6291,13 +6658,28 @@
         <v>8</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>166</v>
+        <v>180</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -6305,25 +6687,40 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>169</v>
+        <v>183</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -6331,25 +6728,40 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>171</v>
+        <v>185</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -6357,25 +6769,40 @@
         <v>8</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>174</v>
+        <v>188</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/sampleprojects/Poker/excel/Poker.xlsx
+++ b/sampleprojects/Poker/excel/Poker.xlsx
@@ -12,14 +12,15 @@
     <sheet name="LAG Decision" sheetId="4" r:id="rId7"/>
     <sheet name="Rock Decision" sheetId="5" r:id="rId8"/>
     <sheet name="CallingStation Decision" sheetId="6" r:id="rId9"/>
-    <sheet name="EDD" sheetId="7" r:id="rId10"/>
+    <sheet name="Evaluate All Players" sheetId="7" r:id="rId10"/>
+    <sheet name="EDD" sheetId="8" r:id="rId11"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
   <si>
     <t>DT: Poker Decision</t>
   </si>
@@ -378,6 +379,33 @@
   </si>
   <si>
     <t>Big bet weak hand - fold</t>
+  </si>
+  <si>
+    <t>DT: Evaluate All Players</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENTS: </t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 1410</t>
+  </si>
+  <si>
+    <t>for all game.players</t>
+  </si>
+  <si>
+    <t>Always, for every player in the game</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Decide this player's action using their archetype's table</t>
+  </si>
+  <si>
+    <t>perform Poker_Decision</t>
+  </si>
+  <si>
+    <t>Evaluating {player.name}</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -5786,6 +5814,550 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>3</v>
+      </c>
+      <c r="G14" s="4">
+        <v>4</v>
+      </c>
+      <c r="H14" s="4">
+        <v>5</v>
+      </c>
+      <c r="I14" s="4">
+        <v>6</v>
+      </c>
+      <c r="J14" s="4">
+        <v>7</v>
+      </c>
+      <c r="K14" s="4">
+        <v>8</v>
+      </c>
+      <c r="L14" s="4">
+        <v>9</v>
+      </c>
+      <c r="M14" s="4">
+        <v>10</v>
+      </c>
+      <c r="N14" s="4">
+        <v>11</v>
+      </c>
+      <c r="O14" s="4">
+        <v>12</v>
+      </c>
+      <c r="P14" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>14</v>
+      </c>
+      <c r="R14" s="4">
+        <v>15</v>
+      </c>
+      <c r="S14" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>1</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+      <c r="F17" s="1">
+        <v>3</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4</v>
+      </c>
+      <c r="H17" s="1">
+        <v>5</v>
+      </c>
+      <c r="I17" s="1">
+        <v>6</v>
+      </c>
+      <c r="J17" s="1">
+        <v>7</v>
+      </c>
+      <c r="K17" s="1">
+        <v>8</v>
+      </c>
+      <c r="L17" s="1">
+        <v>9</v>
+      </c>
+      <c r="M17" s="1">
+        <v>10</v>
+      </c>
+      <c r="N17" s="1">
+        <v>11</v>
+      </c>
+      <c r="O17" s="1">
+        <v>12</v>
+      </c>
+      <c r="P17" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>14</v>
+      </c>
+      <c r="R17" s="1">
+        <v>15</v>
+      </c>
+      <c r="S17" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="18"/>
     <col customWidth="true" max="2" min="2" width="25"/>
     <col customWidth="true" max="3" min="3" width="10"/>
@@ -5802,56 +6374,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -5870,10 +6442,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
@@ -5885,10 +6457,10 @@
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -5911,10 +6483,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
@@ -5926,10 +6498,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -5952,10 +6524,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
@@ -5967,10 +6539,10 @@
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -5993,25 +6565,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -6034,10 +6606,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
@@ -6049,10 +6621,10 @@
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -6072,10 +6644,10 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -6094,10 +6666,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
@@ -6109,10 +6681,10 @@
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -6135,25 +6707,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -6176,25 +6748,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -6217,13 +6789,13 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>8</v>
@@ -6232,10 +6804,10 @@
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -6258,10 +6830,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
@@ -6270,13 +6842,13 @@
         <v>8</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -6299,25 +6871,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>150</v>
-      </c>
       <c r="G15" s="8" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -6340,13 +6912,13 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>8</v>
@@ -6355,10 +6927,10 @@
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -6381,25 +6953,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -6419,10 +6991,10 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -6441,25 +7013,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>8</v>
@@ -6482,25 +7054,25 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>8</v>
@@ -6523,25 +7095,25 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>8</v>
@@ -6564,10 +7136,10 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>8</v>
@@ -6576,13 +7148,13 @@
         <v>8</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>8</v>
@@ -6605,25 +7177,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>8</v>
@@ -6646,10 +7218,10 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>8</v>
@@ -6658,13 +7230,13 @@
         <v>8</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>8</v>
@@ -6687,25 +7259,25 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>8</v>
@@ -6728,25 +7300,25 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>8</v>
@@ -6769,25 +7341,25 @@
         <v>8</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>8</v>

--- a/sampleprojects/Poker/excel/Poker.xlsx
+++ b/sampleprojects/Poker/excel/Poker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <si>
     <t>DT: Poker Decision</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>LAG archetype</t>
@@ -1327,13 +1330,13 @@
         <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -1377,22 +1380,22 @@
         <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -1436,22 +1439,22 @@
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
@@ -1495,19 +1498,19 @@
         <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>14</v>
@@ -1551,11 +1554,11 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
@@ -1611,13 +1614,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>8</v>
@@ -1670,16 +1673,16 @@
         <v>2</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>8</v>
@@ -1729,10 +1732,10 @@
         <v>3</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -1741,7 +1744,7 @@
         <v>8</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>8</v>
@@ -1788,10 +1791,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
@@ -1803,7 +1806,7 @@
         <v>8</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>8</v>
@@ -1847,22 +1850,22 @@
         <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>8</v>
@@ -1903,11 +1906,11 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -1963,7 +1966,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>8</v>
@@ -2022,7 +2025,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>8</v>
@@ -2081,7 +2084,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>8</v>
@@ -2140,7 +2143,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>8</v>
@@ -2223,7 +2226,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2246,7 +2249,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2269,7 +2272,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2292,7 +2295,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2425,13 +2428,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>8</v>
@@ -2481,11 +2484,11 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -2541,13 +2544,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>8</v>
@@ -2597,11 +2600,11 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -2657,7 +2660,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>8</v>
@@ -2739,7 +2742,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2785,7 +2788,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2808,7 +2811,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2941,25 +2944,25 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>8</v>
@@ -3000,13 +3003,13 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
@@ -3015,10 +3018,10 @@
         <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>8</v>
@@ -3059,25 +3062,25 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>8</v>
@@ -3118,25 +3121,25 @@
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>8</v>
@@ -3174,11 +3177,11 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -3234,16 +3237,16 @@
         <v>1</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>8</v>
@@ -3293,10 +3296,10 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -3305,7 +3308,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>8</v>
@@ -3352,10 +3355,10 @@
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -3367,7 +3370,7 @@
         <v>8</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>8</v>
@@ -3411,10 +3414,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -3429,7 +3432,7 @@
         <v>8</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>8</v>
@@ -3467,11 +3470,11 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -3527,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>8</v>
@@ -3586,7 +3589,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>8</v>
@@ -3645,7 +3648,7 @@
         <v>3</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>8</v>
@@ -3704,7 +3707,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>8</v>
@@ -3763,7 +3766,7 @@
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>8</v>
@@ -3845,7 +3848,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3891,7 +3894,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -3914,7 +3917,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -4047,22 +4050,22 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>8</v>
@@ -4106,22 +4109,22 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -4165,22 +4168,22 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -4221,11 +4224,11 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -4281,13 +4284,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>8</v>
@@ -4340,16 +4343,16 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>8</v>
@@ -4399,10 +4402,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -4411,7 +4414,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>8</v>
@@ -4458,10 +4461,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -4473,7 +4476,7 @@
         <v>8</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>8</v>
@@ -4514,11 +4517,11 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -4574,7 +4577,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>8</v>
@@ -4633,7 +4636,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>8</v>
@@ -4692,7 +4695,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>8</v>
@@ -4751,7 +4754,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>8</v>
@@ -4833,7 +4836,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4879,7 +4882,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -4902,7 +4905,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -5035,22 +5038,22 @@
         <v>1</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>8</v>
@@ -5094,22 +5097,22 @@
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -5153,22 +5156,22 @@
         <v>3</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -5209,11 +5212,11 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -5269,13 +5272,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>8</v>
@@ -5328,16 +5331,16 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>8</v>
@@ -5387,10 +5390,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -5399,7 +5402,7 @@
         <v>8</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>8</v>
@@ -5446,10 +5449,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -5461,7 +5464,7 @@
         <v>8</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>8</v>
@@ -5502,11 +5505,11 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -5562,7 +5565,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>8</v>
@@ -5621,7 +5624,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>8</v>
@@ -5680,7 +5683,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>8</v>
@@ -5739,7 +5742,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>8</v>
@@ -5821,7 +5824,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5867,7 +5870,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -5890,7 +5893,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -5944,7 +5947,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -6050,10 +6053,10 @@
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -6106,11 +6109,11 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -6166,13 +6169,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>8</v>
@@ -6222,11 +6225,11 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -6282,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>8</v>
@@ -6374,56 +6377,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -6442,10 +6445,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
@@ -6457,10 +6460,10 @@
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -6483,10 +6486,10 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
@@ -6498,10 +6501,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -6524,10 +6527,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
@@ -6539,10 +6542,10 @@
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -6565,25 +6568,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -6606,10 +6609,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
@@ -6621,10 +6624,10 @@
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -6644,10 +6647,10 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -6666,10 +6669,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
@@ -6681,10 +6684,10 @@
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -6707,25 +6710,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -6748,25 +6751,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -6789,13 +6792,13 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>8</v>
@@ -6804,10 +6807,10 @@
         <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -6830,10 +6833,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
@@ -6842,13 +6845,13 @@
         <v>8</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -6871,25 +6874,25 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -6912,13 +6915,13 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>8</v>
@@ -6927,10 +6930,10 @@
         <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -6953,25 +6956,25 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -6991,10 +6994,10 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -7013,25 +7016,25 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>8</v>
@@ -7054,25 +7057,25 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>8</v>
@@ -7095,25 +7098,25 @@
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>8</v>
@@ -7136,10 +7139,10 @@
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>8</v>
@@ -7148,13 +7151,13 @@
         <v>8</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>8</v>
@@ -7177,25 +7180,25 @@
         <v>8</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>8</v>
@@ -7218,10 +7221,10 @@
         <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>8</v>
@@ -7230,13 +7233,13 @@
         <v>8</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>8</v>
@@ -7259,25 +7262,25 @@
         <v>8</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D25" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>8</v>
@@ -7300,25 +7303,25 @@
         <v>8</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>8</v>
@@ -7341,25 +7344,25 @@
         <v>8</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>8</v>
